--- a/samples/D_应收票据备查簿.xlsx
+++ b/samples/D_应收票据备查簿.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>库存</t>
+          <t>已兑付</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -578,7 +578,11 @@
       <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>已到期兑付</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -619,7 +623,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>库存</t>
+          <t>已兑付</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -635,7 +639,11 @@
       <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>已到期兑付</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -676,7 +684,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>库存</t>
+          <t>已兑付</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -694,7 +702,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>信用等级较低</t>
+          <t>已到期兑付</t>
         </is>
       </c>
     </row>
@@ -755,7 +763,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>已终止确认</t>
+          <t>已终止确认，贴现息12,400元</t>
         </is>
       </c>
     </row>
@@ -934,7 +942,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>逾期未兑付!需转应收并计提坏账</t>
+          <t>逾期未兑付!需转应收账款并计提坏账</t>
         </is>
       </c>
     </row>
